--- a/examples/きふわらべオンリー即売会_参加サークル一覧.xlsx
+++ b/examples/きふわらべオンリー即売会_参加サークル一覧.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\muzudho\CircleSpaceCoordinator\Docs\素材\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\muzudho\CircleSpaceCoordinator\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F30BF0C-E84F-442A-84AD-43176BD0A81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8B8FDC-76FA-42D0-B4FB-A06239BEF174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5630" yWindow="-20700" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7110" yWindow="-21280" windowWidth="33730" windowHeight="20450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -643,7 +643,7 @@
       <c r="H3">
         <v>70</v>
       </c>
-      <c r="I3" t="b">
+      <c r="I3">
         <v>1</v>
       </c>
     </row>
@@ -805,7 +805,7 @@
       <c r="H12">
         <v>50</v>
       </c>
-      <c r="I12" t="b">
+      <c r="I12">
         <v>1</v>
       </c>
     </row>
@@ -879,7 +879,7 @@
       <c r="H16">
         <v>150</v>
       </c>
-      <c r="I16" t="b">
+      <c r="I16">
         <v>1</v>
       </c>
     </row>
@@ -987,7 +987,7 @@
       <c r="H22">
         <v>80</v>
       </c>
-      <c r="I22" t="b">
+      <c r="I22">
         <v>1</v>
       </c>
     </row>

--- a/examples/きふわらべオンリー即売会_参加サークル一覧.xlsx
+++ b/examples/きふわらべオンリー即売会_参加サークル一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\muzudho\CircleSpaceCoordinator\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8B8FDC-76FA-42D0-B4FB-A06239BEF174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253EC81B-94DE-40C9-9851-3B8C1FA64602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7110" yWindow="-21280" windowWidth="33730" windowHeight="20450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="324" yWindow="216" windowWidth="17856" windowHeight="13164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>区画記号</t>
     <rPh sb="0" eb="2">
@@ -214,6 +214,214 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>カクトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>代表者名</t>
+    <rPh sb="0" eb="3">
+      <t>ダイヒョウシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>むずでょ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒井</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白田</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤川</t>
+    <rPh sb="0" eb="2">
+      <t>アカガワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黄山</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>橙河</t>
+    <rPh sb="0" eb="1">
+      <t>ダイダイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>緑沢</t>
+    <rPh sb="0" eb="1">
+      <t>ミドリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>サワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水辺</t>
+    <rPh sb="0" eb="2">
+      <t>ミズベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青谷</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>タニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紺木</t>
+    <rPh sb="0" eb="1">
+      <t>コン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>藍崎</t>
+    <rPh sb="0" eb="1">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫野</t>
+    <rPh sb="0" eb="1">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桃部</t>
+    <rPh sb="0" eb="1">
+      <t>モモ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灰下</t>
+    <rPh sb="0" eb="1">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銀原</t>
+    <rPh sb="0" eb="1">
+      <t>ギン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金上</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>茶地</t>
+    <rPh sb="0" eb="1">
+      <t>チャ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>透藤</t>
+    <rPh sb="0" eb="1">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>フジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒼村</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紅本</t>
+    <rPh sb="0" eb="1">
+      <t>クレナイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>緋塚</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -568,20 +776,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.5" customWidth="1"/>
     <col min="2" max="2" width="9.796875" customWidth="1"/>
     <col min="3" max="3" width="13.69921875" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.796875" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" customWidth="1"/>
-    <col min="7" max="7" width="17.09765625" customWidth="1"/>
-    <col min="8" max="9" width="10.796875" customWidth="1"/>
+    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" customWidth="1"/>
+    <col min="8" max="8" width="17.09765625" customWidth="1"/>
+    <col min="9" max="10" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -595,22 +804,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="C2">
         <v>1001</v>
       </c>
@@ -618,16 +830,19 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="C3">
         <v>1002</v>
       </c>
@@ -635,19 +850,22 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
         <v>31</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>70</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4">
         <v>1003</v>
       </c>
@@ -655,16 +873,19 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="C5">
         <v>1004</v>
       </c>
@@ -672,16 +893,19 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="C6">
         <v>1005</v>
       </c>
@@ -689,19 +913,22 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>1013</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="C7">
         <v>1006</v>
       </c>
@@ -709,19 +936,22 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>1018</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="C8">
         <v>1007</v>
       </c>
@@ -729,16 +959,19 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="C9">
         <v>1008</v>
       </c>
@@ -746,16 +979,19 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
         <v>37</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="H9">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="C10">
         <v>1009</v>
       </c>
@@ -763,16 +999,19 @@
         <v>17</v>
       </c>
       <c r="E10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
         <v>35</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="H10">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="I10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="C11">
         <v>1010</v>
       </c>
@@ -780,16 +1019,19 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="H11">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="C12">
         <v>1011</v>
       </c>
@@ -797,19 +1039,22 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="H12">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>50</v>
       </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="C13">
         <v>1012</v>
       </c>
@@ -817,16 +1062,19 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="H13">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="C14">
         <v>1013</v>
       </c>
@@ -834,19 +1082,22 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
         <v>34</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
       <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
         <v>1005</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10">
       <c r="C15">
         <v>1014</v>
       </c>
@@ -854,16 +1105,19 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
         <v>35</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="H15">
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="I15">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="C16">
         <v>1015</v>
       </c>
@@ -871,19 +1125,22 @@
         <v>23</v>
       </c>
       <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" t="s">
         <v>35</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="H16">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="I16">
         <v>150</v>
       </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9">
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10">
       <c r="C17">
         <v>1016</v>
       </c>
@@ -891,16 +1148,19 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" t="s">
         <v>34</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>2</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:9">
+    <row r="18" spans="3:10">
       <c r="C18">
         <v>1017</v>
       </c>
@@ -908,16 +1168,19 @@
         <v>25</v>
       </c>
       <c r="E18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s">
         <v>39</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>2</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="3:9">
+    <row r="19" spans="3:10">
       <c r="C19">
         <v>1018</v>
       </c>
@@ -925,19 +1188,22 @@
         <v>26</v>
       </c>
       <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
       <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
         <v>1006</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="3:9">
+    <row r="20" spans="3:10">
       <c r="C20">
         <v>1019</v>
       </c>
@@ -945,16 +1211,19 @@
         <v>27</v>
       </c>
       <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" t="s">
         <v>31</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="H20">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="I20">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="3:9">
+    <row r="21" spans="3:10">
       <c r="C21">
         <v>1020</v>
       </c>
@@ -962,16 +1231,19 @@
         <v>28</v>
       </c>
       <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="H21">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="I21">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:9">
+    <row r="22" spans="3:10">
       <c r="C22">
         <v>1021</v>
       </c>
@@ -979,20 +1251,24 @@
         <v>29</v>
       </c>
       <c r="E22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" t="s">
         <v>31</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="H22">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="I22">
         <v>80</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>